--- a/filesystem/Finance/Billing/FenwickGenomics_Nov2025_statement.xlsx
+++ b/filesystem/Finance/Billing/FenwickGenomics_Nov2025_statement.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00;(&quot;$&quot;#,##0.00)"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00;(&quot;$&quot;#,##0.00);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -189,6 +189,33 @@
     <font>
       <name val="Segoe UI"/>
       <color rgb="000284C7"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF475569"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF475569"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF475569"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF475569"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF1E40AF"/>
       <sz val="9.5"/>
     </font>
   </fonts>
@@ -262,7 +289,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -392,11 +419,163 @@
         <color rgb="006EE7B7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="0093C5FD"/>
+      </right>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="0093C5FD"/>
+      </right>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="006EE7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="006EE7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="006EE7B7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="006EE7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="006EE7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="006EE7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="006EE7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="006EE7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="001E293B"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="001E293B"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001E293B"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -548,6 +727,31 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -876,98 +1080,49 @@
           <t>Thornfield Life Sciences Marketing, Inc.</t>
         </is>
       </c>
-      <c r="B1" s="18" t="n"/>
-      <c r="C1" s="18" t="n"/>
-      <c r="D1" s="18" t="n"/>
-      <c r="E1" s="18" t="n"/>
-      <c r="F1" s="18" t="n"/>
-      <c r="G1" s="18" t="n"/>
-      <c r="H1" s="18" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>Monthly Billing Statement</t>
         </is>
       </c>
-      <c r="B2" s="19" t="n"/>
-      <c r="C2" s="19" t="n"/>
-      <c r="D2" s="19" t="n"/>
-      <c r="E2" s="19" t="n"/>
-      <c r="F2" s="19" t="n"/>
-      <c r="G2" s="19" t="n"/>
-      <c r="H2" s="19" t="n"/>
     </row>
     <row r="3" ht="12" customHeight="1"/>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>227 Alexander Drive, Suite 400</t>
         </is>
       </c>
-      <c r="B4" s="20" t="n"/>
-      <c r="C4" s="20" t="n"/>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="20" t="n"/>
-      <c r="F4" s="20" t="n"/>
-      <c r="G4" s="20" t="n"/>
-      <c r="H4" s="20" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="54" t="inlineStr">
         <is>
           <t>Durham, NC 27709</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n"/>
-      <c r="C5" s="20" t="n"/>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="20" t="n"/>
-      <c r="H5" s="20" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="54" t="inlineStr">
         <is>
           <t>EIN: 47-3812905</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n"/>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="20" t="n"/>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="20" t="n"/>
-      <c r="G6" s="20" t="n"/>
-      <c r="H6" s="20" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="54" t="inlineStr">
         <is>
           <t>Phone: +1 (919) 555-0142</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n"/>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="20" t="n"/>
-      <c r="E7" s="20" t="n"/>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="20" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="54" t="inlineStr">
         <is>
           <t>billing@thornfieldlsm.com</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n"/>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="20" t="n"/>
-      <c r="H8" s="20" t="n"/>
     </row>
     <row r="9" ht="12" customHeight="1"/>
     <row r="10" ht="24" customHeight="1">
@@ -976,13 +1131,13 @@
           <t>Statement</t>
         </is>
       </c>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
-      <c r="G10" s="21" t="n"/>
-      <c r="H10" s="21" t="n"/>
+      <c r="B10" s="55" t="n"/>
+      <c r="C10" s="55" t="n"/>
+      <c r="D10" s="55" t="n"/>
+      <c r="E10" s="55" t="n"/>
+      <c r="F10" s="55" t="n"/>
+      <c r="G10" s="55" t="n"/>
+      <c r="H10" s="55" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
@@ -995,12 +1150,12 @@
           <t>STMT-2025-11-0198</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="23" t="n"/>
-      <c r="F11" s="23" t="n"/>
-      <c r="G11" s="23" t="n"/>
-      <c r="H11" s="23" t="n"/>
+      <c r="C11" s="56" t="n"/>
+      <c r="D11" s="56" t="n"/>
+      <c r="E11" s="56" t="n"/>
+      <c r="F11" s="56" t="n"/>
+      <c r="G11" s="56" t="n"/>
+      <c r="H11" s="57" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="22" t="inlineStr">
@@ -1013,12 +1168,12 @@
           <t>11/01/2025</t>
         </is>
       </c>
-      <c r="C12" s="23" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="23" t="n"/>
-      <c r="F12" s="23" t="n"/>
-      <c r="G12" s="23" t="n"/>
-      <c r="H12" s="23" t="n"/>
+      <c r="C12" s="56" t="n"/>
+      <c r="D12" s="56" t="n"/>
+      <c r="E12" s="56" t="n"/>
+      <c r="F12" s="56" t="n"/>
+      <c r="G12" s="56" t="n"/>
+      <c r="H12" s="57" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="22" t="inlineStr">
@@ -1031,12 +1186,12 @@
           <t>11/01/2025 – 11/30/2025</t>
         </is>
       </c>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="23" t="n"/>
-      <c r="G13" s="23" t="n"/>
-      <c r="H13" s="23" t="n"/>
+      <c r="C13" s="56" t="n"/>
+      <c r="D13" s="56" t="n"/>
+      <c r="E13" s="56" t="n"/>
+      <c r="F13" s="56" t="n"/>
+      <c r="G13" s="56" t="n"/>
+      <c r="H13" s="57" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="22" t="inlineStr">
@@ -1049,12 +1204,12 @@
           <t>November 2025</t>
         </is>
       </c>
-      <c r="C14" s="23" t="n"/>
-      <c r="D14" s="23" t="n"/>
-      <c r="E14" s="23" t="n"/>
-      <c r="F14" s="23" t="n"/>
-      <c r="G14" s="23" t="n"/>
-      <c r="H14" s="23" t="n"/>
+      <c r="C14" s="56" t="n"/>
+      <c r="D14" s="56" t="n"/>
+      <c r="E14" s="56" t="n"/>
+      <c r="F14" s="56" t="n"/>
+      <c r="G14" s="56" t="n"/>
+      <c r="H14" s="57" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="22" t="inlineStr">
@@ -1067,12 +1222,12 @@
           <t>Net 30</t>
         </is>
       </c>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="23" t="n"/>
-      <c r="F15" s="23" t="n"/>
-      <c r="G15" s="23" t="n"/>
-      <c r="H15" s="23" t="n"/>
+      <c r="C15" s="56" t="n"/>
+      <c r="D15" s="56" t="n"/>
+      <c r="E15" s="56" t="n"/>
+      <c r="F15" s="56" t="n"/>
+      <c r="G15" s="56" t="n"/>
+      <c r="H15" s="57" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="22" t="inlineStr">
@@ -1085,12 +1240,12 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="C16" s="23" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="23" t="n"/>
-      <c r="F16" s="23" t="n"/>
-      <c r="G16" s="23" t="n"/>
-      <c r="H16" s="23" t="n"/>
+      <c r="C16" s="56" t="n"/>
+      <c r="D16" s="56" t="n"/>
+      <c r="E16" s="56" t="n"/>
+      <c r="F16" s="56" t="n"/>
+      <c r="G16" s="56" t="n"/>
+      <c r="H16" s="57" t="n"/>
     </row>
     <row r="17" ht="12" customHeight="1"/>
     <row r="18" ht="24" customHeight="1">
@@ -1099,13 +1254,13 @@
           <t>Bill To</t>
         </is>
       </c>
-      <c r="B18" s="21" t="n"/>
-      <c r="C18" s="21" t="n"/>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="21" t="n"/>
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="21" t="n"/>
+      <c r="B18" s="55" t="n"/>
+      <c r="C18" s="55" t="n"/>
+      <c r="D18" s="55" t="n"/>
+      <c r="E18" s="55" t="n"/>
+      <c r="F18" s="55" t="n"/>
+      <c r="G18" s="55" t="n"/>
+      <c r="H18" s="55" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="22" t="inlineStr">
@@ -1118,12 +1273,12 @@
           <t>Fenwick Genomics, Inc.</t>
         </is>
       </c>
-      <c r="C19" s="23" t="n"/>
-      <c r="D19" s="23" t="n"/>
-      <c r="E19" s="23" t="n"/>
-      <c r="F19" s="23" t="n"/>
-      <c r="G19" s="23" t="n"/>
-      <c r="H19" s="23" t="n"/>
+      <c r="C19" s="56" t="n"/>
+      <c r="D19" s="56" t="n"/>
+      <c r="E19" s="56" t="n"/>
+      <c r="F19" s="56" t="n"/>
+      <c r="G19" s="56" t="n"/>
+      <c r="H19" s="57" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="22" t="inlineStr">
@@ -1136,12 +1291,12 @@
           <t>Waltham, MA</t>
         </is>
       </c>
-      <c r="C20" s="23" t="n"/>
-      <c r="D20" s="23" t="n"/>
-      <c r="E20" s="23" t="n"/>
-      <c r="F20" s="23" t="n"/>
-      <c r="G20" s="23" t="n"/>
-      <c r="H20" s="23" t="n"/>
+      <c r="C20" s="56" t="n"/>
+      <c r="D20" s="56" t="n"/>
+      <c r="E20" s="56" t="n"/>
+      <c r="F20" s="56" t="n"/>
+      <c r="G20" s="56" t="n"/>
+      <c r="H20" s="57" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="22" t="inlineStr">
@@ -1154,12 +1309,12 @@
           <t>CUST-2025-0198</t>
         </is>
       </c>
-      <c r="C21" s="23" t="n"/>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="23" t="n"/>
-      <c r="F21" s="23" t="n"/>
-      <c r="G21" s="23" t="n"/>
-      <c r="H21" s="23" t="n"/>
+      <c r="C21" s="56" t="n"/>
+      <c r="D21" s="56" t="n"/>
+      <c r="E21" s="56" t="n"/>
+      <c r="F21" s="56" t="n"/>
+      <c r="G21" s="56" t="n"/>
+      <c r="H21" s="57" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="22" t="inlineStr">
@@ -1172,12 +1327,12 @@
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="C22" s="23" t="n"/>
-      <c r="D22" s="23" t="n"/>
-      <c r="E22" s="23" t="n"/>
-      <c r="F22" s="23" t="n"/>
-      <c r="G22" s="23" t="n"/>
-      <c r="H22" s="23" t="n"/>
+      <c r="C22" s="56" t="n"/>
+      <c r="D22" s="56" t="n"/>
+      <c r="E22" s="56" t="n"/>
+      <c r="F22" s="56" t="n"/>
+      <c r="G22" s="56" t="n"/>
+      <c r="H22" s="57" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="22" t="inlineStr">
@@ -1190,12 +1345,12 @@
           <t>SO-2025-0417</t>
         </is>
       </c>
-      <c r="C23" s="23" t="n"/>
-      <c r="D23" s="23" t="n"/>
-      <c r="E23" s="23" t="n"/>
-      <c r="F23" s="23" t="n"/>
-      <c r="G23" s="23" t="n"/>
-      <c r="H23" s="23" t="n"/>
+      <c r="C23" s="56" t="n"/>
+      <c r="D23" s="56" t="n"/>
+      <c r="E23" s="56" t="n"/>
+      <c r="F23" s="56" t="n"/>
+      <c r="G23" s="56" t="n"/>
+      <c r="H23" s="57" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="22" t="inlineStr">
@@ -1208,12 +1363,12 @@
           <t>04/01/2025 – 03/31/2026</t>
         </is>
       </c>
-      <c r="C24" s="23" t="n"/>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="n"/>
-      <c r="F24" s="23" t="n"/>
-      <c r="G24" s="23" t="n"/>
-      <c r="H24" s="23" t="n"/>
+      <c r="C24" s="56" t="n"/>
+      <c r="D24" s="56" t="n"/>
+      <c r="E24" s="56" t="n"/>
+      <c r="F24" s="56" t="n"/>
+      <c r="G24" s="56" t="n"/>
+      <c r="H24" s="57" t="n"/>
     </row>
     <row r="25" ht="12" customHeight="1"/>
     <row r="26" ht="24" customHeight="1">
@@ -1222,13 +1377,13 @@
           <t>Line Items</t>
         </is>
       </c>
-      <c r="B26" s="21" t="n"/>
-      <c r="C26" s="21" t="n"/>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
-      <c r="F26" s="21" t="n"/>
-      <c r="G26" s="21" t="n"/>
-      <c r="H26" s="21" t="n"/>
+      <c r="B26" s="55" t="n"/>
+      <c r="C26" s="55" t="n"/>
+      <c r="D26" s="55" t="n"/>
+      <c r="E26" s="55" t="n"/>
+      <c r="F26" s="55" t="n"/>
+      <c r="G26" s="55" t="n"/>
+      <c r="H26" s="55" t="n"/>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
@@ -1341,7 +1496,7 @@
       <c r="F29" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="34" t="inlineStr">
+      <c r="G29" s="58" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1381,7 +1536,7 @@
       <c r="F30" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="34" t="inlineStr">
+      <c r="G30" s="58" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1421,7 +1576,7 @@
       <c r="F31" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="34" t="inlineStr">
+      <c r="G31" s="58" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1461,7 +1616,7 @@
       <c r="F32" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="34" t="inlineStr">
+      <c r="G32" s="58" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1501,7 +1656,7 @@
       <c r="F33" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="34" t="inlineStr">
+      <c r="G33" s="58" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1541,7 +1696,7 @@
       <c r="F34" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="34" t="inlineStr">
+      <c r="G34" s="58" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1581,7 +1736,7 @@
       <c r="F35" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="34" t="inlineStr">
+      <c r="G35" s="58" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1599,13 +1754,13 @@
           <t>Statement Total</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n"/>
-      <c r="C37" s="21" t="n"/>
-      <c r="D37" s="21" t="n"/>
-      <c r="E37" s="21" t="n"/>
-      <c r="F37" s="21" t="n"/>
-      <c r="G37" s="21" t="n"/>
-      <c r="H37" s="21" t="n"/>
+      <c r="B37" s="55" t="n"/>
+      <c r="C37" s="55" t="n"/>
+      <c r="D37" s="55" t="n"/>
+      <c r="E37" s="55" t="n"/>
+      <c r="F37" s="55" t="n"/>
+      <c r="G37" s="55" t="n"/>
+      <c r="H37" s="55" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="22" t="inlineStr">
@@ -1613,15 +1768,15 @@
           <t>Subtotal — Retainer</t>
         </is>
       </c>
-      <c r="B38" s="22" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="22" t="n"/>
+      <c r="B38" s="56" t="n"/>
+      <c r="C38" s="56" t="n"/>
+      <c r="D38" s="56" t="n"/>
+      <c r="E38" s="57" t="n"/>
       <c r="F38" s="36" t="n">
         <v>8500</v>
       </c>
-      <c r="G38" s="37" t="n"/>
-      <c r="H38" s="37" t="n"/>
+      <c r="G38" s="56" t="n"/>
+      <c r="H38" s="57" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="38" t="inlineStr">
@@ -1629,15 +1784,15 @@
           <t>Subtotal — Reimbursables</t>
         </is>
       </c>
-      <c r="B39" s="38" t="n"/>
-      <c r="C39" s="38" t="n"/>
-      <c r="D39" s="38" t="n"/>
-      <c r="E39" s="38" t="n"/>
-      <c r="F39" s="39" t="n">
+      <c r="B39" s="56" t="n"/>
+      <c r="C39" s="56" t="n"/>
+      <c r="D39" s="56" t="n"/>
+      <c r="E39" s="57" t="n"/>
+      <c r="F39" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="40" t="n"/>
-      <c r="H39" s="40" t="n"/>
+      <c r="G39" s="56" t="n"/>
+      <c r="H39" s="57" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="38" t="inlineStr">
@@ -1645,15 +1800,15 @@
           <t>Adjustments</t>
         </is>
       </c>
-      <c r="B40" s="38" t="n"/>
-      <c r="C40" s="38" t="n"/>
-      <c r="D40" s="38" t="n"/>
-      <c r="E40" s="38" t="n"/>
-      <c r="F40" s="39" t="n">
+      <c r="B40" s="56" t="n"/>
+      <c r="C40" s="56" t="n"/>
+      <c r="D40" s="56" t="n"/>
+      <c r="E40" s="57" t="n"/>
+      <c r="F40" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="40" t="n"/>
-      <c r="H40" s="40" t="n"/>
+      <c r="G40" s="56" t="n"/>
+      <c r="H40" s="57" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="41" t="inlineStr">
@@ -1661,15 +1816,15 @@
           <t>Total Due for November 2025</t>
         </is>
       </c>
-      <c r="B41" s="41" t="n"/>
-      <c r="C41" s="41" t="n"/>
-      <c r="D41" s="41" t="n"/>
-      <c r="E41" s="41" t="n"/>
+      <c r="B41" s="60" t="n"/>
+      <c r="C41" s="60" t="n"/>
+      <c r="D41" s="60" t="n"/>
+      <c r="E41" s="61" t="n"/>
       <c r="F41" s="42" t="n">
         <v>8500</v>
       </c>
-      <c r="G41" s="43" t="n"/>
-      <c r="H41" s="43" t="n"/>
+      <c r="G41" s="60" t="n"/>
+      <c r="H41" s="61" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="22" t="inlineStr">
@@ -1677,15 +1832,15 @@
           <t>Payments Received</t>
         </is>
       </c>
-      <c r="B42" s="22" t="n"/>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="22" t="n"/>
-      <c r="E42" s="22" t="n"/>
+      <c r="B42" s="56" t="n"/>
+      <c r="C42" s="56" t="n"/>
+      <c r="D42" s="56" t="n"/>
+      <c r="E42" s="57" t="n"/>
       <c r="F42" s="36" t="n">
         <v>-8500</v>
       </c>
-      <c r="G42" s="37" t="n"/>
-      <c r="H42" s="37" t="n"/>
+      <c r="G42" s="56" t="n"/>
+      <c r="H42" s="57" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
@@ -1693,15 +1848,15 @@
           <t>Balance</t>
         </is>
       </c>
-      <c r="B43" s="44" t="n"/>
-      <c r="C43" s="44" t="n"/>
-      <c r="D43" s="44" t="n"/>
-      <c r="E43" s="44" t="n"/>
+      <c r="B43" s="62" t="n"/>
+      <c r="C43" s="62" t="n"/>
+      <c r="D43" s="62" t="n"/>
+      <c r="E43" s="63" t="n"/>
       <c r="F43" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="46" t="n"/>
-      <c r="H43" s="46" t="n"/>
+      <c r="G43" s="62" t="n"/>
+      <c r="H43" s="63" t="n"/>
     </row>
     <row r="44" ht="12" customHeight="1"/>
     <row r="45" ht="28" customHeight="1">
@@ -1710,13 +1865,13 @@
           <t>Remittance confirmed via ACH on 11/03/2025. No balance carried into December cycle.</t>
         </is>
       </c>
-      <c r="B45" s="47" t="n"/>
-      <c r="C45" s="47" t="n"/>
-      <c r="D45" s="47" t="n"/>
-      <c r="E45" s="47" t="n"/>
-      <c r="F45" s="47" t="n"/>
-      <c r="G45" s="47" t="n"/>
-      <c r="H45" s="47" t="n"/>
+      <c r="B45" s="62" t="n"/>
+      <c r="C45" s="62" t="n"/>
+      <c r="D45" s="62" t="n"/>
+      <c r="E45" s="62" t="n"/>
+      <c r="F45" s="62" t="n"/>
+      <c r="G45" s="62" t="n"/>
+      <c r="H45" s="63" t="n"/>
     </row>
     <row r="46" ht="12" customHeight="1"/>
     <row r="47" ht="24" customHeight="1">
@@ -1725,13 +1880,13 @@
           <t>Remittance &amp; Reference</t>
         </is>
       </c>
-      <c r="B47" s="21" t="n"/>
-      <c r="C47" s="21" t="n"/>
-      <c r="D47" s="21" t="n"/>
-      <c r="E47" s="21" t="n"/>
-      <c r="F47" s="21" t="n"/>
-      <c r="G47" s="21" t="n"/>
-      <c r="H47" s="21" t="n"/>
+      <c r="B47" s="55" t="n"/>
+      <c r="C47" s="55" t="n"/>
+      <c r="D47" s="55" t="n"/>
+      <c r="E47" s="55" t="n"/>
+      <c r="F47" s="55" t="n"/>
+      <c r="G47" s="55" t="n"/>
+      <c r="H47" s="55" t="n"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="48" t="inlineStr">
@@ -1739,13 +1894,6 @@
           <t>• Remit to: Thornfield Life Sciences Marketing, Inc., Attn: Accounts Receivable, 227 Alexander Drive, Suite 400, Durham, NC 27709</t>
         </is>
       </c>
-      <c r="B48" s="48" t="n"/>
-      <c r="C48" s="48" t="n"/>
-      <c r="D48" s="48" t="n"/>
-      <c r="E48" s="48" t="n"/>
-      <c r="F48" s="48" t="n"/>
-      <c r="G48" s="48" t="n"/>
-      <c r="H48" s="48" t="n"/>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="48" t="inlineStr">
@@ -1753,13 +1901,6 @@
           <t>• ERPNext Sales Order: SO-2025-0417</t>
         </is>
       </c>
-      <c r="B49" s="48" t="n"/>
-      <c r="C49" s="48" t="n"/>
-      <c r="D49" s="48" t="n"/>
-      <c r="E49" s="48" t="n"/>
-      <c r="F49" s="48" t="n"/>
-      <c r="G49" s="48" t="n"/>
-      <c r="H49" s="48" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="48" t="inlineStr">
@@ -1767,13 +1908,6 @@
           <t>• ERPNext Customer ID: CUST-2025-0198</t>
         </is>
       </c>
-      <c r="B50" s="48" t="n"/>
-      <c r="C50" s="48" t="n"/>
-      <c r="D50" s="48" t="n"/>
-      <c r="E50" s="48" t="n"/>
-      <c r="F50" s="48" t="n"/>
-      <c r="G50" s="48" t="n"/>
-      <c r="H50" s="48" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="48" t="inlineStr">
@@ -1781,17 +1915,10 @@
           <t>• Invoice questions: alan.rutherford@thornfieldlsm.com</t>
         </is>
       </c>
-      <c r="B51" s="48" t="n"/>
-      <c r="C51" s="48" t="n"/>
-      <c r="D51" s="48" t="n"/>
-      <c r="E51" s="48" t="n"/>
-      <c r="F51" s="48" t="n"/>
-      <c r="G51" s="48" t="n"/>
-      <c r="H51" s="48" t="n"/>
     </row>
     <row r="52" ht="12" customHeight="1"/>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="49" t="inlineStr">
+      <c r="A53" s="64" t="inlineStr">
         <is>
           <t>Prepared by:</t>
         </is>
@@ -1819,7 +1946,7 @@
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="52" t="inlineStr">
+      <c r="A57" s="65" t="inlineStr">
         <is>
           <t>alan.rutherford@thornfieldlsm.com</t>
         </is>
